--- a/naver-place-crawler/results_hair/청라_미용실.xlsx
+++ b/naver-place-crawler/results_hair/청라_미용실.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>시새움</t>
+          <t>26도헤어 청라점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tjdgh1400@naver.com</t>
+          <t>beasj75@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1443-1460</t>
+          <t>0507-1414-5377</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 B109호, B110호</t>
+          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 304호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjdgh1400</t>
+          <t>https://www.instagram.com/26_hair_vol.15/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1177</v>
+        <v>5616</v>
       </c>
       <c r="Q2" t="n">
-        <v>98</v>
+        <v>821</v>
       </c>
       <c r="R2" t="n">
-        <v>1275</v>
+        <v>6437</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,47 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1920971232</t>
+          <t>1054687814</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1920971232</t>
+          <t>https://m.place.naver.com/place/1054687814</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>디얼스 청라커낼점</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>블루클럽 청라신도시점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>jacob_studio93@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1497-5111</t>
+          <t>032-565-0410</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 2층</t>
+          <t>인천광역시 서구 청라라임로 85</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dears_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -707,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5465</v>
+        <v>159</v>
       </c>
       <c r="Q3" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>5569</v>
+        <v>166</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1727610245</t>
+          <t>88126852</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1727610245</t>
+          <t>https://m.place.naver.com/place/88126852</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뮤엠헤어 인천청라점</t>
+          <t>에이바헤어 청라커낼점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>muu_m@naver.com</t>
+          <t>dpdnjs3594@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1390-9028</t>
+          <t>0507-1354-6838</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 지하1층 a11호, a12호</t>
+          <t>인천광역시 서구 청라커낼로 264 두손중앙프라자 205호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muu.m0517/</t>
+          <t>https://www.instagram.com/avahair_6838</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>644</v>
+        <v>2946</v>
       </c>
       <c r="Q4" t="n">
-        <v>58</v>
+        <v>5800</v>
       </c>
       <c r="R4" t="n">
-        <v>702</v>
+        <v>8746</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1242780534</t>
+          <t>1111577805</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1242780534</t>
+          <t>https://m.place.naver.com/place/1111577805</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리안헤어 청라호수공원점</t>
+          <t>리안헤어 인천가정루원시티점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>riahn2580@naver.com</t>
+          <t>asd79762@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1433-2582</t>
+          <t>0507-1473-0780</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로74번길 31 206호</t>
+          <t>인천광역시 서구 청중로478번길 24 에스디프라자 201호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/riahn2580</t>
+          <t>https://blog.naver.com/asd79762</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14549</v>
+        <v>1732</v>
       </c>
       <c r="Q5" t="n">
-        <v>5872</v>
+        <v>54</v>
       </c>
       <c r="R5" t="n">
-        <v>20421</v>
+        <v>1786</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>821832336</t>
+          <t>1763422647</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/821832336</t>
+          <t>https://m.place.naver.com/place/1763422647</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고정현헤어 청라1호점</t>
+          <t>멘스트 맨즈헤어 루원시티본점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gohair7@naver.com</t>
+          <t>gmldyd6364@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1423-3257</t>
+          <t>0507-1413-8337</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 19 홍익파크 2층</t>
+          <t>인천광역시 서구 염곡로464번길 11 1층 113호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.gohair.co.kr</t>
+          <t>https://www.instagram.com/menst_do2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -973,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>7921</v>
+        <v>403</v>
       </c>
       <c r="Q6" t="n">
-        <v>962</v>
+        <v>158</v>
       </c>
       <c r="R6" t="n">
-        <v>8883</v>
+        <v>561</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>35880109</t>
+          <t>2075307891</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35880109</t>
+          <t>https://m.place.naver.com/place/2075307891</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에이바헤어 청라커낼점</t>
+          <t>살롱마치 청라점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dpdnjs3594@naver.com</t>
+          <t>march_gajihye@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1354-6838</t>
+          <t>0507-1318-0316</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 264 두손중앙프라자 205호</t>
+          <t>인천광역시 서구 청라에메랄드로41번길 15 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/avahair_6838</t>
+          <t>https://www.instagram.com/salonmarch_gajihye</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2902</v>
+        <v>7808</v>
       </c>
       <c r="Q7" t="n">
-        <v>5549</v>
+        <v>393</v>
       </c>
       <c r="R7" t="n">
-        <v>8451</v>
+        <v>8201</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1111577805</t>
+          <t>1835982875</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111577805</t>
+          <t>https://m.place.naver.com/place/1835982875</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라콘헤어 청라점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ckstnehd@naver.com</t>
-        </is>
-      </c>
+          <t>수이헤어</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1374-2338</t>
+          <t>0507-1448-1677</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 255호</t>
+          <t>인천광역시 서구 청라루비로144번길 22 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ckstnehd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1619</v>
+        <v>881</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1659</v>
+        <v>883</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1688200599</t>
+          <t>1156213767</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688200599</t>
+          <t>https://m.place.naver.com/place/1156213767</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1218,35 +1218,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>919맨즈헤어</t>
+          <t>골든헤어컷</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1428-5753</t>
+          <t>0507-1477-6705</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로100번길 8-28 2층 201,202호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-31 A동 2층 204호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@hairman57</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>609</v>
+        <v>281</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="R9" t="n">
-        <v>649</v>
+        <v>359</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1548562435</t>
+          <t>1951465702</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1548562435</t>
+          <t>https://m.place.naver.com/place/1951465702</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1308,44 +1308,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>이철헤어커커 루원시티점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>kerker2327@naver.com</t>
-        </is>
-      </c>
+          <t>살롱드고</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1302-2326</t>
+          <t>0507-1339-0227</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재3로 115 HB타워 2층 201호, 202호</t>
+          <t>인천광역시 서구 청라커낼로 300 판매5동104호 *스타벅스옆*</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://leechulhairkerker.co.kr/</t>
+          <t>https://www.instagram.com/salonde_ko/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1356,7 +1352,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2222</v>
+        <v>1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>1226</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>3448</v>
+        <v>1989</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1976700186</t>
+          <t>1589512491</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1976700186</t>
+          <t>https://m.place.naver.com/place/1589512491</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1455,13 +1451,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R11" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1480,7 +1476,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1488,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>리엔제이헤어 청라본점</t>
+          <t>드디어헤어 청라점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ghgus2714@naver.com</t>
+          <t>psc_banhada@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1364-6934</t>
+          <t>0507-1426-9155</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 11 208호</t>
+          <t>인천광역시 서구 청라한내로 110 A동 2층 208호, 209호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leenj_hairsalon</t>
+          <t>https://blog.naver.com/psc_banhada</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1529,7 +1525,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1545,17 +1541,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1438</v>
+        <v>843</v>
       </c>
       <c r="Q12" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="R12" t="n">
-        <v>1565</v>
+        <v>893</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1619466775</t>
+          <t>1428570155</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619466775</t>
+          <t>https://m.place.naver.com/place/1428570155</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1582,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>고정현헤어 청라2호점</t>
+          <t>청라미용실 펌킨하우스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gohair7@naver.com</t>
+          <t>ddaeun1116@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1316-3256</t>
+          <t>0507-1406-4028</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 16 키움프라자 2층</t>
+          <t>인천광역시 서구 중봉대로586번길 9-4 쓰리엠타워 4층 404호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://www.gohair.co.kr</t>
+          <t>https://blog.naver.com/ddaeun1116</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1643,13 +1639,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5843</v>
+        <v>600</v>
       </c>
       <c r="Q13" t="n">
-        <v>977</v>
+        <v>141</v>
       </c>
       <c r="R13" t="n">
-        <v>6820</v>
+        <v>741</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1654,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1607502409</t>
+          <t>38549843</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1607502409</t>
+          <t>https://m.place.naver.com/place/38549843</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1676,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>라라비긴헤어 가정점</t>
+          <t>살롱드더별</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tjswhddlf961@naver.com</t>
+          <t>dodobaby22@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1492-6660</t>
+          <t>0507-1388-1665</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 16-1 203</t>
+          <t>인천광역시 서구 중봉대로612번길 10-22 우리프라자 살롱드더별</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/lalabegin_hyuna_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1712,7 +1708,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1733,17 +1729,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1694</v>
+        <v>512</v>
       </c>
       <c r="Q14" t="n">
-        <v>1451</v>
+        <v>35</v>
       </c>
       <c r="R14" t="n">
-        <v>3145</v>
+        <v>547</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1748,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1447377305</t>
+          <t>1177312788</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447377305</t>
+          <t>https://m.place.naver.com/place/1177312788</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1827,13 +1823,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1852,7 +1848,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1864,29 +1860,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>험블디자이어</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>flochuu@naver.com</t>
-        </is>
-      </c>
+          <t>프롬미헤어</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1421-6668</t>
+          <t>0507-1328-9131</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 1층 108호</t>
+          <t>인천광역시 서구 청라커낼로319번길 3-3 102호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flochuu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1896,12 +1888,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1917,17 +1909,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>767</v>
+        <v>188</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>808</v>
+        <v>190</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1928,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1743181913</t>
+          <t>2051397129</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743181913</t>
+          <t>https://m.place.naver.com/place/2051397129</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1958,29 +1950,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>청라미용실 펌킨하우스</t>
+          <t>고정현헤어 청라1호점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ddaeun1116@naver.com</t>
+          <t>gohair7@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1406-4028</t>
+          <t>0507-1423-3257</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-4 쓰리엠타워 4층 404호</t>
+          <t>인천광역시 서구 중봉대로586번길 19 홍익파크 2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ddaeun1116</t>
+          <t>http://www.gohair.co.kr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2015,13 +2007,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>598</v>
+        <v>7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>141</v>
+        <v>1001</v>
       </c>
       <c r="R17" t="n">
-        <v>739</v>
+        <v>8936</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>38549843</t>
+          <t>35880109</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38549843</t>
+          <t>https://m.place.naver.com/place/35880109</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2044,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>온어블 청라본점</t>
+          <t>뮤엠헤어 인천청라점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nsscent@naver.com</t>
+          <t>muu_m@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1371-5813</t>
+          <t>0507-1390-9028</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 A동 B1층 A19호 온어블헤어</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 지하1층 a11호, a12호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/onable.official</t>
+          <t>https://www.instagram.com/muu.m0517/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,13 +2101,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1864</v>
+        <v>648</v>
       </c>
       <c r="Q18" t="n">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="R18" t="n">
-        <v>1975</v>
+        <v>707</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2116,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1088155978</t>
+          <t>1242780534</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088155978</t>
+          <t>https://m.place.naver.com/place/1242780534</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2146,29 +2138,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>상미헤어 청라스퀘어7점</t>
+          <t>온어블 청라본점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sangmihair@naver.com</t>
+          <t>nsscent@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1338-8896</t>
+          <t>0507-1371-5813</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 76 2층 238호,239호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 커낼에비뉴 A동 B1층 A19호 온어블헤어</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sangmihair</t>
+          <t>https://www.instagram.com/onable.official</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2183,7 +2175,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2203,13 +2195,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1962</v>
+        <v>1867</v>
       </c>
       <c r="Q19" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="R19" t="n">
-        <v>2069</v>
+        <v>1949</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2210,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1973500967</t>
+          <t>1088155978</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973500967</t>
+          <t>https://m.place.naver.com/place/1088155978</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2232,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>오늘 반헤어</t>
+          <t>오르빗헤어</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dhsmf610@naver.com</t>
+          <t>kanghj0426@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1336-6793</t>
+          <t>0507-1374-5207</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 서구 옥빛로15번길 1 1층 102호</t>
+          <t>인천광역시 서구 염곡로 468 102호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/y_u___93/?next=%2F</t>
+          <t>https://www.instagram.com/orbit__hair</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2297,13 +2289,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>429</v>
+        <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="R20" t="n">
-        <v>450</v>
+        <v>191</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2304,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1467609213</t>
+          <t>2037381163</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1467609213</t>
+          <t>https://m.place.naver.com/place/2037381163</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2334,30 +2326,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>살롱프롬디</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>이철헤어커커 루원시티점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>kerker2327@naver.com</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>032-569-0130</t>
+          <t>0507-1302-2326</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 127 1층 살롱프롬디</t>
+          <t>인천광역시 서구 봉오재3로 115 HB타워 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://leechulhairkerker.co.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2367,7 +2363,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2378,22 +2374,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>720</v>
+        <v>2271</v>
       </c>
       <c r="Q21" t="n">
-        <v>76</v>
+        <v>1247</v>
       </c>
       <c r="R21" t="n">
-        <v>796</v>
+        <v>3518</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2402,17 +2398,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1459456648</t>
+          <t>1976700186</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1459456648</t>
+          <t>https://m.place.naver.com/place/1976700186</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2424,25 +2420,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>고정현헤어 루원시티점</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>고정현헤어 청라2호점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gohair7@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>032-506-3256</t>
+          <t>0507-1316-3256</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 437 sk리더스뷰상가 B301동 B116호</t>
+          <t>인천광역시 서구 청라커낼로288번길 16 키움프라자 2층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.gohair.co.kr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2473,17 +2473,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3412</v>
+        <v>5865</v>
       </c>
       <c r="Q22" t="n">
-        <v>800</v>
+        <v>1026</v>
       </c>
       <c r="R22" t="n">
-        <v>4212</v>
+        <v>6891</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2492,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1745919374</t>
+          <t>1607502409</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1745919374</t>
+          <t>https://m.place.naver.com/place/1607502409</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2514,29 +2514,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>헤어 에이블룸</t>
+          <t>로이드밤 인천청라점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hairabloom@naver.com</t>
+          <t>lloydbomb23@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1309-0734</t>
+          <t>0507-1305-6945</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로76번길 7 헤어에이블룸 2층</t>
+          <t>인천광역시 서구 중봉대로 588 센트럴프라자 2층 204호 로이드밤 인천청라점</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hair.a.bloom</t>
+          <t>https://blog.naver.com/lloydbomb23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1264</v>
+        <v>1909</v>
       </c>
       <c r="Q23" t="n">
-        <v>213</v>
+        <v>42</v>
       </c>
       <c r="R23" t="n">
-        <v>1477</v>
+        <v>1951</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2586,17 +2586,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1879742835</t>
+          <t>1954660935</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1879742835</t>
+          <t>https://m.place.naver.com/place/1954660935</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2608,29 +2608,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>보그헤어 청라커낼점</t>
+          <t>헤어베이 청라점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wjddnjs4172@naver.com</t>
+          <t>159wngml@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1465-5780</t>
+          <t>0507-1376-7409</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 264 1층 119호, 120호</t>
+          <t>인천광역시 서구 청라한내로 90 MK뷰 405호 헤어베이 청라점</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dr_gayago</t>
+          <t>https://blog.naver.com/159wngml</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>967</v>
+        <v>1707</v>
       </c>
       <c r="Q24" t="n">
-        <v>918</v>
+        <v>297</v>
       </c>
       <c r="R24" t="n">
-        <v>1885</v>
+        <v>2004</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2680,17 +2680,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1086679047</t>
+          <t>1087204612</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086679047</t>
+          <t>https://m.place.naver.com/place/1087204612</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2702,29 +2702,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>리안헤어 청라커낼점</t>
+          <t>보그헤어 청라커낼점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>riahnhaircheongna@naver.com</t>
+          <t>wjddnjs4172@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1431-3061</t>
+          <t>0507-1465-5780</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 79 A83호 리안헤어</t>
+          <t>인천광역시 서구 청라커낼로 264 1층 119호, 120호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/riahnhaircheongna</t>
+          <t>https://www.instagram.com/dr_gayago</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>17262</v>
+        <v>1004</v>
       </c>
       <c r="Q25" t="n">
-        <v>6835</v>
+        <v>821</v>
       </c>
       <c r="R25" t="n">
-        <v>24097</v>
+        <v>1825</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2774,17 +2774,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1088626431</t>
+          <t>1086679047</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088626431</t>
+          <t>https://m.place.naver.com/place/1086679047</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2796,25 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>골든헤어컷</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>살롱드담 가정 루원시티점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>salondedaam@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1477-6705</t>
+          <t>0507-1395-1209</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-31 A동 2층 204호</t>
+          <t>인천광역시 서구 염곡로464번길 7 2층 살롱드담</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/salon_de_daam</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2824,7 +2828,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2845,17 +2849,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>262</v>
+        <v>610</v>
       </c>
       <c r="Q26" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
-        <v>340</v>
+        <v>631</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2868,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1951465702</t>
+          <t>2051547214</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951465702</t>
+          <t>https://m.place.naver.com/place/2051547214</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2886,48 +2890,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>루이헤어</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>lui_hair@naver.com</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>헤어레브</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1498-0201</t>
+          <t>0507-1401-4246</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 17 힐데스하임 상가1층 루이헤어</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 228호, 229호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/107161</t>
+          <t>https://www.instagram.com/hairreve_/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2947,13 +2943,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2038</v>
+        <v>650</v>
       </c>
       <c r="Q27" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="R27" t="n">
-        <v>2136</v>
+        <v>718</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2958,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1773242142</t>
+          <t>1003756037</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1773242142</t>
+          <t>https://m.place.naver.com/place/1003756037</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2984,29 +2980,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>티지헤어살롱 청라점</t>
+          <t>미주노헤어 청라본점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>tigihairlala@naver.com</t>
+          <t>bettylove510@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1355-1286</t>
+          <t>0507-1391-4233</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 2층 티지헤어살롱 청라점</t>
+          <t>인천광역시 서구 청라에메랄드로 99 지젤엠청라 A동 2층 15,16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tigihairlala</t>
+          <t>http://www.instagram.com/mijuno.official</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3021,7 +3017,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3041,13 +3037,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1175</v>
+        <v>4493</v>
       </c>
       <c r="Q28" t="n">
-        <v>307</v>
+        <v>1799</v>
       </c>
       <c r="R28" t="n">
-        <v>1482</v>
+        <v>6292</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3052,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1601889074</t>
+          <t>1031360168</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1601889074</t>
+          <t>https://m.place.naver.com/place/1031360168</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3078,29 +3074,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>고움헤어살롱</t>
+          <t>리안헤어 청라커낼점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>balguhair@naver.com</t>
+          <t>riahnhaircheongna@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1496-5587</t>
+          <t>0507-1431-3061</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 22 청라엑슬루타워 A상가 218호</t>
+          <t>인천광역시 서구 청라에메랄드로 79 A83호 리안헤어</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/balguhair</t>
+          <t>https://blog.naver.com/riahnhaircheongna</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3135,13 +3131,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>341</v>
+        <v>17486</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>7066</v>
       </c>
       <c r="R29" t="n">
-        <v>391</v>
+        <v>24552</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3146,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1688144838</t>
+          <t>1088626431</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688144838</t>
+          <t>https://m.place.naver.com/place/1088626431</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3172,25 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>멘스트 맨즈헤어 루원시티본점</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>살롱드유 청라1호점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wltn3311@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1413-8337</t>
+          <t>0507-1364-0200</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로464번길 11 1층 113호</t>
+          <t>인천광역시 서구 청라커낼로260번길 7-11 3층 305호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/menst_do2</t>
+          <t>https://www.instagram.com/salon_de.you</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3225,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>372</v>
+        <v>518</v>
       </c>
       <c r="Q30" t="n">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="R30" t="n">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3240,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2075307891</t>
+          <t>1102114772</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2075307891</t>
+          <t>https://m.place.naver.com/place/1102114772</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3262,30 +3262,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>미주노헤어 청라본점</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>비지에프헤어 가정동 루원시티점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bgfbgf@naver.com</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1391-4233</t>
+          <t>0507-1400-5363</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠청라 A동 2층 15,16</t>
+          <t>인천광역시 서구 염곡로 472 2층 201호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mijuno.official</t>
+          <t>https://talk.naver.com/profile/c/bgfhair</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3300,10 +3304,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3315,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4406</v>
+        <v>3496</v>
       </c>
       <c r="Q31" t="n">
-        <v>1521</v>
+        <v>1264</v>
       </c>
       <c r="R31" t="n">
-        <v>5927</v>
+        <v>4760</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3330,17 +3338,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1031360168</t>
+          <t>21889301</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031360168</t>
+          <t>https://m.place.naver.com/place/21889301</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3352,29 +3360,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>로이드밤 인천청라점</t>
+          <t>라비앙르로즈 청라점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lloydbomb23@naver.com</t>
+          <t>sjwjhappy@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1305-6945</t>
+          <t>0507-1373-6543</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 588 센트럴프라자 2층 204호 로이드밤 인천청라점</t>
+          <t>인천광역시 서구 중봉대로612번길 10 209호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lloydbomb23</t>
+          <t>https://www.instagram.com/lavieenr_rose/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3389,7 +3397,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3405,17 +3413,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1900</v>
+        <v>3326</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>836</v>
       </c>
       <c r="R32" t="n">
-        <v>1942</v>
+        <v>4162</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3424,17 +3432,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1954660935</t>
+          <t>1897468640</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954660935</t>
+          <t>https://m.place.naver.com/place/1897468640</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3446,29 +3454,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>토리헤어 청라점</t>
+          <t>H STYLE 헤어살롱 청라 3동점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>zs1561@naver.com</t>
+          <t>cmarto@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1427-6769</t>
+          <t>032-562-9093</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 9-11 청라매그놀리아 3층 토리헤어</t>
+          <t>인천광역시 서구 푸른로16번길 17 1층 미용실</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zs1561</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3478,12 +3486,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3503,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1983</v>
+        <v>361</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="R33" t="n">
-        <v>2009</v>
+        <v>429</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3518,17 +3526,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1670445268</t>
+          <t>596911819</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670445268</t>
+          <t>https://m.place.naver.com/place/596911819</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3540,29 +3548,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>헤어작공</t>
+          <t>시새움</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>hairjk@naver.com</t>
+          <t>tjdgh1400@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1491-5337</t>
+          <t>0507-1443-1460</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 8-10 1층 117호 헤어작공</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 B109호, B110호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hairjk</t>
+          <t>https://blog.naver.com/tjdgh1400</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3597,13 +3605,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>657</v>
+        <v>1191</v>
       </c>
       <c r="Q34" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R34" t="n">
-        <v>751</v>
+        <v>1289</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3612,17 +3620,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1079245563</t>
+          <t>1920971232</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1079245563</t>
+          <t>https://m.place.naver.com/place/1920971232</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3634,29 +3642,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>살롱드고</t>
+          <t>에이엔센트 청라점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shs292@naver.com</t>
+          <t>sosg4854@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1339-0227</t>
+          <t>0507-1350-7019</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 판매5동104호 *스타벅스옆*</t>
+          <t>인천광역시 서구 청라커낼로288번길 26 상가 102동 234호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salonde_ko/</t>
+          <t>http://www.youtube.com/@김가빈-m6d2j</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3691,13 +3699,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1971</v>
+        <v>690</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>261</v>
       </c>
       <c r="R35" t="n">
-        <v>1978</v>
+        <v>951</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3706,17 +3714,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1589512491</t>
+          <t>1285080360</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1589512491</t>
+          <t>https://m.place.naver.com/place/1285080360</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3728,29 +3736,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>청라헤어 헤드스파 본점</t>
+          <t>템드헤어룸 루원시티점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>qazxswqaz147@naver.com</t>
+          <t>1288jh@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1374-7494</t>
+          <t>0507-1444-1050</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 131 중흥에스클래스 상가동 105호</t>
+          <t>인천광역시 서구 봉오재3로110번길 7 가정봄프라자 2층 204호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cheongna_hair_spa</t>
+          <t>https://www.instagram.com/temd_by.sooho</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3785,13 +3793,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>375</v>
+        <v>1964</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>202</v>
       </c>
       <c r="R36" t="n">
-        <v>383</v>
+        <v>2166</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3800,17 +3808,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1447243775</t>
+          <t>1262827062</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1447243775</t>
+          <t>https://m.place.naver.com/place/1262827062</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3822,25 +3830,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>리브헤어 오쏘헤어</t>
+          <t>아문헤어 인천청라점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ji____woo@naver.com</t>
+          <t>lovemi717@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>032-562-5004</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 지젤엠 2층 중앙엘레베이터 바로앞</t>
+          <t>인천광역시 서구 청라커낼로 277 B1층 B103호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ji____woo</t>
+          <t>https://www.instagram.com/a_moon_official</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3855,7 +3867,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3875,13 +3887,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>405</v>
+        <v>543</v>
       </c>
       <c r="Q37" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="R37" t="n">
-        <v>527</v>
+        <v>652</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3890,17 +3902,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1569136658</t>
+          <t>1638145673</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1569136658</t>
+          <t>https://m.place.naver.com/place/1638145673</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3912,29 +3924,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2U헤어</t>
+          <t>모하제이 청라점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>wjdeodjq62@naver.com</t>
+          <t>google-_-b@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>032-576-2221</t>
+          <t>0507-1358-8032</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 봉오재1로 15 루원시티 대성베르힐 동문상가 1층 106호 2u헤어</t>
+          <t>인천광역시 서구 차오름로 25 2층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://instagram.com/2uhair_</t>
+          <t>https://www.instagram.com/mohaj_cheongna</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3969,13 +3981,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>589</v>
+        <v>3214</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="R38" t="n">
-        <v>591</v>
+        <v>3308</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +3996,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1595252878</t>
+          <t>1008031770</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1595252878</t>
+          <t>https://m.place.naver.com/place/1008031770</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4006,29 +4018,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>샵208 청라점</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>jjkker9179@naver.com</t>
-        </is>
-      </c>
+          <t>미주노헤어 청라2호점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1333-0208</t>
+          <t>0507-1415-4533</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 판매5동 208호</t>
+          <t>인천광역시 서구 청라커낼로 264 청라두손중앙프라자 305호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jjkker9179</t>
+          <t>http://www.instagram.com/mijuno.official</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4043,7 +4051,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4063,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>338</v>
+        <v>1152</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="R39" t="n">
-        <v>356</v>
+        <v>1353</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,17 +4086,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1264651642</t>
+          <t>1846417705</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264651642</t>
+          <t>https://m.place.naver.com/place/1846417705</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4100,29 +4108,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>라비앙르로즈 청라점</t>
+          <t>박승철헤어스투디오 청라라임타워점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sjwjhappy@naver.com</t>
+          <t>pschair04@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1373-6543</t>
+          <t>032-562-4753</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 209호</t>
+          <t>인천광역시 서구 청라라임로 65 라임타워 2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lavieenr_rose/</t>
+          <t>https://blog.naver.com/pschair04</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4137,7 +4145,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4148,7 +4156,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4157,13 +4165,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3299</v>
+        <v>7588</v>
       </c>
       <c r="Q40" t="n">
-        <v>884</v>
+        <v>1371</v>
       </c>
       <c r="R40" t="n">
-        <v>4183</v>
+        <v>8959</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4172,17 +4180,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1897468640</t>
+          <t>35149965</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1897468640</t>
+          <t>https://m.place.naver.com/place/35149965</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4194,29 +4202,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>모하제이 청라점</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>google-_-b@naver.com</t>
-        </is>
-      </c>
+          <t>고정현헤어 루원시티점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1358-8032</t>
+          <t>032-506-3256</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 차오름로 25 2층</t>
+          <t>인천광역시 서구 가정로 437 sk리더스뷰상가 B301동 B116호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mohaj_cheongna</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4226,7 +4230,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4247,17 +4251,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3133</v>
+        <v>3424</v>
       </c>
       <c r="Q41" t="n">
-        <v>94</v>
+        <v>845</v>
       </c>
       <c r="R41" t="n">
-        <v>3227</v>
+        <v>4269</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4266,17 +4270,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1008031770</t>
+          <t>1745919374</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1008031770</t>
+          <t>https://m.place.naver.com/place/1745919374</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4288,29 +4292,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>살롱드더별</t>
+          <t>험블디자이어</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dodobaby22@naver.com</t>
+          <t>flochuu@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1388-1665</t>
+          <t>0507-1421-6668</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-22 우리프라자 살롱드더별</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 판매3동 1층 108호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/flochuu</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4320,12 +4324,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4341,17 +4345,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>507</v>
+        <v>769</v>
       </c>
       <c r="Q42" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="R42" t="n">
-        <v>542</v>
+        <v>810</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4360,17 +4364,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1177312788</t>
+          <t>1743181913</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1177312788</t>
+          <t>https://m.place.naver.com/place/1743181913</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4382,25 +4386,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>미주노헤어 청라2호점</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>헤어 에이블룸</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>hairabloom@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1415-4533</t>
+          <t>0507-1309-0734</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 264 청라두손중앙프라자 305호</t>
+          <t>인천광역시 서구 청라에메랄드로76번길 7 헤어에이블룸 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mijuno.official</t>
+          <t>https://www.instagram.com/hair.a.bloom</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4435,13 +4443,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1149</v>
+        <v>1266</v>
       </c>
       <c r="Q43" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="R43" t="n">
-        <v>1352</v>
+        <v>1479</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4450,17 +4458,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1846417705</t>
+          <t>1879742835</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1846417705</t>
+          <t>https://m.place.naver.com/place/1879742835</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4472,29 +4480,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>마이위프</t>
+          <t>카이정헤어 인천청라점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>my_whiff@naver.com</t>
+          <t>kaijung11@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1323-2836</t>
+          <t>0507-1481-0151</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-31 A동 2층 215호</t>
+          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 2층 210호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuwol.d___/</t>
+          <t>https://youtube.com/channel/UCZURnxox0laAqOaNmA9KJYg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4529,13 +4537,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>624</v>
+        <v>8404</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>870</v>
       </c>
       <c r="R44" t="n">
-        <v>628</v>
+        <v>9274</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4544,17 +4552,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1871926089</t>
+          <t>1761969092</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1871926089</t>
+          <t>https://m.place.naver.com/place/1761969092</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4566,29 +4574,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>드디어헤어 청라점</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>psc_banhada@naver.com</t>
-        </is>
-      </c>
+          <t>오브미헤어</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1426-9155</t>
+          <t>0507-1325-4403</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 110 A동 2층 208호, 209호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 1층 111호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/psc_banhada</t>
+          <t>https://www.instagram.com/of_mi_/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4603,7 +4607,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4619,17 +4623,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>833</v>
+        <v>285</v>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="R45" t="n">
-        <v>883</v>
+        <v>328</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4638,17 +4642,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1428570155</t>
+          <t>1939238907</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428570155</t>
+          <t>https://m.place.naver.com/place/1939238907</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4660,29 +4664,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>헤어베이 청라점</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>159wngml@naver.com</t>
-        </is>
-      </c>
+          <t>유은헤어</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1376-7409</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로 90 MK뷰 405호 헤어베이 청라점</t>
+          <t>인천광역시 서구 청라대로 131 2층 217호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/159wngml</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4692,12 +4688,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4713,17 +4709,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1685</v>
+        <v>101</v>
       </c>
       <c r="Q46" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1981</v>
+        <v>101</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4732,17 +4728,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1087204612</t>
+          <t>2080331035</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1087204612</t>
+          <t>https://m.place.naver.com/place/2080331035</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4754,25 +4750,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>헤어레브</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>헤어작공</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>hairjk@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1401-4246</t>
+          <t>0507-1491-5337</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로260번길 27 2층 228호, 229호</t>
+          <t>인천광역시 서구 청라커낼로288번길 8-10 1층 117호 헤어작공</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hairreve_/</t>
+          <t>https://blog.naver.com/hairjk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="Q47" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="R47" t="n">
-        <v>711</v>
+        <v>757</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4822,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1003756037</t>
+          <t>1079245563</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003756037</t>
+          <t>https://m.place.naver.com/place/1079245563</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4844,29 +4844,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>땅콩헤어샵</t>
+          <t>티지헤어살롱 청라점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tisse9@naver.com</t>
+          <t>tigihairlala@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1309-6284</t>
+          <t>0507-1355-1286</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 B동 지1층 97호</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 더스페이스타워 2층 티지헤어살롱 청라점</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bagsoyeon6273</t>
+          <t>https://blog.naver.com/tigihairlala</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>723</v>
+        <v>1177</v>
       </c>
       <c r="Q48" t="n">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="R48" t="n">
-        <v>792</v>
+        <v>1482</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1043213741</t>
+          <t>1601889074</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043213741</t>
+          <t>https://m.place.naver.com/place/1601889074</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4938,25 +4938,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>딜라이트헤어</t>
+          <t>디얼스 청라커낼점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1348-3470</t>
+          <t>0507-1497-5111</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로498번안길 20 202호</t>
+          <t>인천광역시 서구 청라커낼로288번길 10 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dears_official</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4987,17 +4987,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>137</v>
+        <v>5667</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="R49" t="n">
-        <v>189</v>
+        <v>5771</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5006,17 +5006,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1068936264</t>
+          <t>1727610245</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068936264</t>
+          <t>https://m.place.naver.com/place/1727610245</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5028,44 +5028,48 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>여운</t>
+          <t>루이헤어</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>subinok@naver.com</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>lui_hair@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1388-3614</t>
+          <t>0507-1498-0201</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 지하1층 비 108호, 지하 1층</t>
+          <t>인천광역시 서구 청라라임로 17 힐데스하임 상가1층 루이헤어</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://instagram.com/afterglow_yunseon</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/107161</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5085,13 +5089,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>538</v>
+        <v>2040</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="R50" t="n">
-        <v>580</v>
+        <v>2138</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5100,17 +5104,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1018913449</t>
+          <t>1773242142</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018913449</t>
+          <t>https://m.place.naver.com/place/1773242142</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5122,20 +5126,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>오르톤헤어</t>
+          <t>살롱프롬디</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1393-2117</t>
+          <t>032-569-0130</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로233번길 3-4 1층 일부(102)호</t>
+          <t>인천광역시 서구 청라에메랄드로 127 1층 살롱프롬디</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5175,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>61</v>
+        <v>726</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="R51" t="n">
-        <v>86</v>
+        <v>802</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5190,17 +5194,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2078751734</t>
+          <t>1459456648</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2078751734</t>
+          <t>https://m.place.naver.com/place/1459456648</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5212,25 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>아벨라움 인천청라점</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>919맨즈헤어</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gksthftla@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1313-3729</t>
+          <t>0507-1428-5753</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로 78 엘림존 201호, 202호</t>
+          <t>인천광역시 서구 청라한내로100번길 8-28 2층 201,202호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/abelraum_cr</t>
+          <t>https://youtube.com/@hairman57</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5265,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>15999</v>
+        <v>610</v>
       </c>
       <c r="Q52" t="n">
-        <v>6927</v>
+        <v>40</v>
       </c>
       <c r="R52" t="n">
-        <v>22926</v>
+        <v>650</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5280,17 +5288,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1432492852</t>
+          <t>1548562435</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1432492852</t>
+          <t>https://m.place.naver.com/place/1548562435</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5302,29 +5310,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>아르봄</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>arbom-@naver.com</t>
-        </is>
-      </c>
+          <t>아벨라움 청라커낼웨이점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1437-1075</t>
+          <t>0507-1335-5347</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로 594 청라비전프라자 2층 202호</t>
+          <t>인천광역시 서구 청라라임로 85 상가A동 ,2층 아벨라움(abelraum)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arbom-</t>
+          <t>https://www.instagram.com/abelraum_4ten</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5339,7 +5343,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5359,13 +5363,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1255</v>
+        <v>2310</v>
       </c>
       <c r="Q53" t="n">
-        <v>120</v>
+        <v>7398</v>
       </c>
       <c r="R53" t="n">
-        <v>1375</v>
+        <v>9708</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5374,17 +5378,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1513553978</t>
+          <t>2049726941</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513553978</t>
+          <t>https://m.place.naver.com/place/2049726941</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5396,29 +5400,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>리안헤어 인천가정루원시티점</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>asd79762@naver.com</t>
-        </is>
-      </c>
+          <t>비다주헤어 청라점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1473-0780</t>
+          <t>0507-1473-0309</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청중로478번길 24 에스디프라자 201호</t>
+          <t>인천광역시 서구 청라한내로72번길 23 쓰리엠파크 201호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/asd79762</t>
+          <t>https://www.instagram.com/vidaju_hair</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1728</v>
+        <v>3351</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="R54" t="n">
-        <v>1782</v>
+        <v>3497</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5468,17 +5468,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1763422647</t>
+          <t>1819362995</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1763422647</t>
+          <t>https://m.place.naver.com/place/1819362995</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5490,29 +5490,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>살롱마치 청라점</t>
+          <t>데탕트 인천청라점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>march_gajihye@naver.com</t>
+          <t>cjstld@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1318-0316</t>
+          <t>0507-1449-1677</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로41번길 15 1층</t>
+          <t>인천광역시 서구 청라루비로 99 대우메디피아빌딩 데탕트 인천청라점</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salonmarch_gajihye</t>
+          <t>https://www.instagram.com/detente_sw</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>7798</v>
+        <v>4111</v>
       </c>
       <c r="Q55" t="n">
-        <v>393</v>
+        <v>571</v>
       </c>
       <c r="R55" t="n">
-        <v>8191</v>
+        <v>4682</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5562,17 +5562,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1835982875</t>
+          <t>1706055610</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835982875</t>
+          <t>https://m.place.naver.com/place/1706055610</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5584,29 +5584,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>수이헤어</t>
+          <t>리안헤어 청라호수공원점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>hilty74@naver.com</t>
+          <t>riahn2580@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1448-1677</t>
+          <t>0507-1433-2582</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로144번길 22 1층</t>
+          <t>인천광역시 서구 크리스탈로74번길 31 206호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/riahn2580</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>875</v>
+        <v>14693</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>6053</v>
       </c>
       <c r="R56" t="n">
-        <v>876</v>
+        <v>20746</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5656,17 +5656,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1156213767</t>
+          <t>821832336</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156213767</t>
+          <t>https://m.place.naver.com/place/821832336</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5678,29 +5678,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 청라라임타워점</t>
+          <t>블랑디헤어 청라본점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pschair04@naver.com</t>
+          <t>sm970510@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>032-562-4753</t>
+          <t>0507-1434-5689</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 65 라임타워 2층</t>
+          <t>인천광역시 서구 크리스탈로102번길 22 1층 블랑디헤어</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pschair04</t>
+          <t>https://www.instagram.com/blanc_d_sumin/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5726,7 +5726,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5735,13 +5735,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7556</v>
+        <v>6766</v>
       </c>
       <c r="Q57" t="n">
-        <v>1371</v>
+        <v>370</v>
       </c>
       <c r="R57" t="n">
-        <v>8927</v>
+        <v>7136</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5750,17 +5750,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>35149965</t>
+          <t>1256981061</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35149965</t>
+          <t>https://m.place.naver.com/place/1256981061</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5772,29 +5772,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아문헤어 인천청라점</t>
+          <t>리엔제이헤어 청라본점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>lovemi717@naver.com</t>
+          <t>ghgus2714@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1423-5012</t>
+          <t>0507-1364-6934</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 277 B1층 B103호</t>
+          <t>인천광역시 서구 청라커낼로260번길 11 208호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a_moon_official</t>
+          <t>https://www.instagram.com/leenj_hairsalon</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>544</v>
+        <v>1438</v>
       </c>
       <c r="Q58" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="R58" t="n">
-        <v>653</v>
+        <v>1565</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5844,17 +5844,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1638145673</t>
+          <t>1619466775</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1638145673</t>
+          <t>https://m.place.naver.com/place/1619466775</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5866,29 +5866,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>데탕트 인천청라점</t>
+          <t>토리헤어 청라점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>cjstld@naver.com</t>
+          <t>zs1561@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1449-1677</t>
+          <t>0507-1427-6769</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라루비로 99 대우메디피아빌딩 데탕트 인천청라점</t>
+          <t>인천광역시 서구 중봉대로586번길 9-11 청라매그놀리아 3층 토리헤어</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/detente_sw</t>
+          <t>https://blog.naver.com/zs1561</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5919,17 +5919,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>4073</v>
+        <v>1995</v>
       </c>
       <c r="Q59" t="n">
-        <v>581</v>
+        <v>26</v>
       </c>
       <c r="R59" t="n">
-        <v>4654</v>
+        <v>2021</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5938,17 +5938,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1706055610</t>
+          <t>1670445268</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1706055610</t>
+          <t>https://m.place.naver.com/place/1670445268</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6017,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3156</v>
+        <v>3169</v>
       </c>
       <c r="Q60" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="R60" t="n">
-        <v>3369</v>
+        <v>3390</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6054,29 +6054,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>예원살롱</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>qkrdldpdnjsz@naver.com</t>
-        </is>
-      </c>
+          <t>살롱드헨느 청라 본점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1308-9879</t>
+          <t>0507-1485-9798</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 푸른로16번길 19 1층 예원살롱</t>
+          <t>인천광역시 서구 청라루비로144번길 23 엠그레이하우스 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeah___wonh</t>
+          <t>https://youtube.com/channel/UC9EWdhMXB4WJdh_IkOba5Lw?si=k_T8Be0iE6dT-54Q</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6107,17 +6103,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>348</v>
+        <v>1065</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>371</v>
+        <v>1069</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6126,17 +6122,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1123310897</t>
+          <t>1924039678</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1123310897</t>
+          <t>https://m.place.naver.com/place/1924039678</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6148,34 +6144,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>카이정헤어 인천청라점</t>
+          <t>라라비긴헤어 가정점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kaijung11@naver.com</t>
+          <t>tjswhddlf961@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1481-0151</t>
+          <t>0507-1492-6660</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10-17 청라타워돔 2층 210호</t>
+          <t>인천광역시 서구 염곡로498번안길 16-1 203</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCZURnxox0laAqOaNmA9KJYg</t>
+          <t>http://www.instagram.com/lalabegin_hyuna_</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6205,13 +6201,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>8166</v>
+        <v>1700</v>
       </c>
       <c r="Q62" t="n">
-        <v>829</v>
+        <v>1482</v>
       </c>
       <c r="R62" t="n">
-        <v>8995</v>
+        <v>3182</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6220,17 +6216,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1761969092</t>
+          <t>1447377305</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1761969092</t>
+          <t>https://m.place.naver.com/place/1447377305</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6242,29 +6238,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오르빗헤어</t>
+          <t>라콘헤어 청라점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kanghj0426@naver.com</t>
+          <t>ckstnehd@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1374-5207</t>
+          <t>0507-1374-2338</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 468 102호</t>
+          <t>인천광역시 서구 청라커낼로260번길 27 2층 255호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orbit__hair</t>
+          <t>https://blog.naver.com/ckstnehd</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6279,7 +6275,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6299,13 +6295,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>142</v>
+        <v>1617</v>
       </c>
       <c r="Q63" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R63" t="n">
-        <v>188</v>
+        <v>1657</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6314,17 +6310,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>2037381163</t>
+          <t>1688200599</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037381163</t>
+          <t>https://m.place.naver.com/place/1688200599</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6336,29 +6332,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>에이엔센트 청라점</t>
+          <t>고움헤어살롱</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sosg4854@naver.com</t>
+          <t>balguhair@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1350-7019</t>
+          <t>0507-1496-5587</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로288번길 26 상가 102동 234호</t>
+          <t>인천광역시 서구 중봉대로586번길 22 청라엑슬루타워 A상가 218호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.youtube.com/@김가빈-m6d2j</t>
+          <t>https://blog.naver.com/balguhair</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6373,7 +6369,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6393,13 +6389,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>678</v>
+        <v>347</v>
       </c>
       <c r="Q64" t="n">
-        <v>186</v>
+        <v>61</v>
       </c>
       <c r="R64" t="n">
-        <v>864</v>
+        <v>408</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6408,17 +6404,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1285080360</t>
+          <t>1688144838</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285080360</t>
+          <t>https://m.place.naver.com/place/1688144838</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6430,29 +6426,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>블랑디헤어 청라본점</t>
+          <t>상미헤어 청라스퀘어7점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sm970510@naver.com</t>
+          <t>sangmihair@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1434-5689</t>
+          <t>0507-1338-8896</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 크리스탈로102번길 22 1층 블랑디헤어</t>
+          <t>인천광역시 서구 청라루비로 76 2층 238호,239호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blanc_d_sumin/</t>
+          <t>https://blog.naver.com/sangmihair</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6467,7 +6463,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6487,13 +6483,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>6711</v>
+        <v>1968</v>
       </c>
       <c r="Q65" t="n">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="R65" t="n">
-        <v>7039</v>
+        <v>2075</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,17 +6498,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1256981061</t>
+          <t>1973500967</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256981061</t>
+          <t>https://m.place.naver.com/place/1973500967</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6524,25 +6520,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>26도헤어 청라점</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>마이위프</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>my_whiff@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1414-5377</t>
+          <t>0507-1323-2836</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 304호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-31 A동 2층 215호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/26_hair_vol.15/</t>
+          <t>https://www.instagram.com/yuwol.d___/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>5539</v>
+        <v>640</v>
       </c>
       <c r="Q66" t="n">
-        <v>855</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>6394</v>
+        <v>644</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6592,17 +6592,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1054687814</t>
+          <t>1871926089</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054687814</t>
+          <t>https://m.place.naver.com/place/1871926089</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6614,25 +6614,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>비다주헤어 청라점</t>
+          <t>나랑헤어살롱</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1473-0309</t>
+          <t>0507-1320-8795</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 23 쓰리엠파크 201호</t>
+          <t>인천광역시 서구 청라에메랄드로 84 1층 102호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vidaju_hair</t>
+          <t>https://www.instagram.com/narang_rola</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6667,13 +6667,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3298</v>
+        <v>1012</v>
       </c>
       <c r="Q67" t="n">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="R67" t="n">
-        <v>3443</v>
+        <v>1030</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6682,17 +6682,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1819362995</t>
+          <t>1906511541</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1819362995</t>
+          <t>https://m.place.naver.com/place/1906511541</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6704,34 +6704,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>비지에프헤어 가정동 루원시티점</t>
+          <t>오늘 반헤어</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bgfbgf@naver.com</t>
+          <t>dhsmf610@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1400-5363</t>
+          <t>0507-1336-6793</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 서구 염곡로 472 2층 201호</t>
+          <t>인천광역시 서구 옥빛로15번길 1 1층 102호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/profile/c/bgfhair</t>
+          <t>https://www.instagram.com/y_u___93/?next=%2F</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6746,14 +6746,10 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -6765,13 +6761,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3485</v>
+        <v>429</v>
       </c>
       <c r="Q68" t="n">
-        <v>1245</v>
+        <v>21</v>
       </c>
       <c r="R68" t="n">
-        <v>4730</v>
+        <v>450</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6780,17 +6776,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>21889301</t>
+          <t>1467609213</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21889301</t>
+          <t>https://m.place.naver.com/place/1467609213</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6802,29 +6798,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아벨라움 청라커낼웨이점</t>
+          <t>아벨라움 인천청라점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>manbizzang@naver.com</t>
+          <t>sbk6751@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1335-5347</t>
+          <t>0507-1313-3729</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라라임로 85 상가A동 ,2층 아벨라움(abelraum)</t>
+          <t>인천광역시 서구 크리스탈로 78 엘림존 201호, 202호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/abelraum_4ten</t>
+          <t>https://www.instagram.com/abelraum_cr</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6859,13 +6855,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2216</v>
+        <v>16224</v>
       </c>
       <c r="Q69" t="n">
-        <v>7139</v>
+        <v>7199</v>
       </c>
       <c r="R69" t="n">
-        <v>9355</v>
+        <v>23423</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6874,51 +6870,51 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>2049726941</t>
+          <t>1432492852</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2049726941</t>
+          <t>https://m.place.naver.com/place/1432492852</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>기와이발소</t>
+          <t>오르톤헤어</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kiwa_barbershop@naver.com</t>
+          <t>dannymam@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1496-1203</t>
+          <t>0507-1393-2117</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 상가 2층 205호</t>
+          <t>인천광역시 서구 청라커낼로233번길 3-4 1층 일부(102)호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kiwa_barbershop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6928,12 +6924,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6949,17 +6945,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>624</v>
+        <v>67</v>
       </c>
       <c r="Q70" t="n">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="R70" t="n">
-        <v>766</v>
+        <v>118</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6968,17 +6964,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1010214058</t>
+          <t>2078751734</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010214058</t>
+          <t>https://m.place.naver.com/place/2078751734</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6990,29 +6986,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>수컷바버샵</t>
+          <t>기와이발소</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>soocutbarbershop@naver.com</t>
+          <t>kiwa_barbershop@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1376-6974</t>
+          <t>0507-1496-1203</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라에메랄드로 99 A동 1층 60호 (지젤엠청라)</t>
+          <t>인천광역시 서구 청라커낼로 300 청라센트럴에일린의뜰 상가 2층 205호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/soocutbarbershop</t>
+          <t>https://blog.naver.com/kiwa_barbershop</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7047,13 +7043,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1489</v>
+        <v>625</v>
       </c>
       <c r="Q71" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="R71" t="n">
-        <v>1598</v>
+        <v>767</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7062,17 +7058,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1688590595</t>
+          <t>1010214058</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1688590595</t>
+          <t>https://m.place.naver.com/place/1010214058</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7084,29 +7080,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>제인바버샵 청라호수공원점</t>
+          <t>FACE바버샵</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>janebarber@naver.com</t>
+          <t>faceluckim@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1491-9770</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라한내로72번길 7-29 B동 309호 제인바버샵 (B동주차)</t>
+          <t>인천광역시 서구 청라커낼로 252 롯데캐슬상가 c동 114호 FACE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jane_barbershop/</t>
+          <t>https://www.instagram.com/wakemeup9am</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7141,13 +7133,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>196</v>
+        <v>1363</v>
       </c>
       <c r="Q72" t="n">
-        <v>99</v>
+        <v>394</v>
       </c>
       <c r="R72" t="n">
-        <v>295</v>
+        <v>1757</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7156,17 +7148,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2081648169</t>
+          <t>1291376883</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2081648169</t>
+          <t>https://m.place.naver.com/place/1291376883</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7235,13 +7227,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="Q73" t="n">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="R73" t="n">
-        <v>1213</v>
+        <v>1231</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7260,7 +7252,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7269,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sienna_blossom@naver.com</t>
+          <t>j_world90@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -7329,13 +7321,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1418</v>
+        <v>1434</v>
       </c>
       <c r="Q74" t="n">
         <v>169</v>
       </c>
       <c r="R74" t="n">
-        <v>1587</v>
+        <v>1603</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7354,7 +7346,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7366,25 +7358,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FACE바버샵</t>
+          <t>부에르바버샵 인천청라점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>faceluckim@naver.com</t>
+          <t>j_170807@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1426-1104</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 청라커낼로 252 롯데캐슬상가 c동 114호 FACE</t>
+          <t>인천광역시 서구 중봉대로612번길 10 206호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wakemeup9am</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7394,7 +7390,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7415,17 +7411,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1361</v>
+        <v>592</v>
       </c>
       <c r="Q75" t="n">
-        <v>394</v>
+        <v>318</v>
       </c>
       <c r="R75" t="n">
-        <v>1755</v>
+        <v>910</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7434,17 +7430,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1291376883</t>
+          <t>1433407928</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1291376883</t>
+          <t>https://m.place.naver.com/place/1433407928</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7456,29 +7452,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>부에르바버샵 인천청라점</t>
+          <t>제인바버샵 청라호수공원점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>j_170807@naver.com</t>
+          <t>janebarber@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1426-1104</t>
+          <t>0507-1491-9770</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로612번길 10 206호</t>
+          <t>인천광역시 서구 청라한내로72번길 7-29 B동 309호 제인바버샵 (B동주차)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jane_barbershop/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7488,7 +7484,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7509,17 +7505,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>591</v>
+        <v>200</v>
       </c>
       <c r="Q76" t="n">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="R76" t="n">
-        <v>904</v>
+        <v>302</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7528,17 +7524,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1433407928</t>
+          <t>2081648169</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433407928</t>
+          <t>https://m.place.naver.com/place/2081648169</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
